--- a/rabbit-web-app/public/sample_excels/trenoops_trailer_sample_file.xlsx
+++ b/rabbit-web-app/public/sample_excels/trenoops_trailer_sample_file.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,12 +421,6 @@
       <c r="G1" t="str">
         <v>year</v>
       </c>
-      <c r="H1" t="str">
-        <v>hoursReading</v>
-      </c>
-      <c r="I1" t="str">
-        <v>oilChangeDate</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -450,16 +444,10 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>